--- a/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
+++ b/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$793</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Resumen (con dato real)'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Resumen (con dato real)'!$A$1:$J$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8921,14 +8921,26 @@
           <t>USD/mes</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>InfoCasas — tipo loft, IVA y expensas incluidos</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr">
         <is>
           <t>2026-08-16</t>
@@ -8936,7 +8948,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Pendiente de relevar.</t>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
@@ -17753,14 +17765,26 @@
           <t>USD/mes</t>
         </is>
       </c>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H427" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="G427" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>InfoCasas</t>
+        </is>
+      </c>
       <c r="I427" t="inlineStr">
         <is>
           <t>2026-08-16</t>
@@ -17768,7 +17792,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Pendiente de relevar.</t>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
@@ -17833,14 +17857,26 @@
           <t>USD/mes</t>
         </is>
       </c>
-      <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H429" t="inlineStr"/>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G429" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>InfoCasas</t>
+        </is>
+      </c>
       <c r="I429" t="inlineStr">
         <is>
           <t>2026-08-16</t>
@@ -17848,7 +17884,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Pendiente de relevar.</t>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
@@ -17873,14 +17909,26 @@
           <t>USD/mes</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H430" t="inlineStr"/>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="G430" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>InfoCasas — Torre Eminent, referencia de techo</t>
+        </is>
+      </c>
       <c r="I430" t="inlineStr">
         <is>
           <t>2026-08-16</t>
@@ -17888,7 +17936,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>Pendiente de relevar.</t>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
@@ -26345,14 +26393,26 @@
           <t>USD/mes</t>
         </is>
       </c>
-      <c r="E640" t="inlineStr"/>
-      <c r="F640" t="inlineStr"/>
-      <c r="G640" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H640" t="inlineStr"/>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="G640" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>InfoCasas — zona de referencia mas economica, dato puntual, no rango</t>
+        </is>
+      </c>
       <c r="I640" t="inlineStr">
         <is>
           <t>2026-08-16</t>
@@ -26360,7 +26420,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>Pendiente de relevar.</t>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
@@ -32496,7 +32556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -32722,17 +32782,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Las Lomas</t>
+          <t>Salvador del Mundo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1 dormitorio</t>
+          <t>Monoambiente</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tradicional (sin muebles)</t>
+          <t>Amoblado (largo plazo)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -32757,7 +32817,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>InfoCasas</t>
+          <t>InfoCasas — tipo loft, IVA y expensas incluidos</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -32779,12 +32839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2 dormitorios</t>
+          <t>1 dormitorio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amoblado (largo plazo)</t>
+          <t>Tradicional (sin muebles)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -32794,12 +32854,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -32826,32 +32886,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Villa Morra</t>
+          <t>Las Lomas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Monoambiente</t>
+          <t>2 dormitorios</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Airbnb / temporal</t>
+          <t>Amoblado (largo plazo)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>USD/noche</t>
+          <t>USD/mes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -32861,7 +32921,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Airbnb (listados directos)</t>
+          <t>InfoCasas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -32888,22 +32948,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amoblado (largo plazo)</t>
+          <t>Airbnb / temporal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>USD/mes</t>
+          <t>USD/noche</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -32913,7 +32973,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>InfoCasas</t>
+          <t>Airbnb (listados directos)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -32935,7 +32995,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2 dormitorios</t>
+          <t>Monoambiente</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -32950,12 +33010,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>800</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1800</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -32987,7 +33047,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3 dormitorios</t>
+          <t>2 dormitorios</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -33002,12 +33062,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -33034,12 +33094,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Villa Morra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1 dormitorio</t>
+          <t>3 dormitorios</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -33054,12 +33114,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -33069,7 +33129,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>InfoCasas — a metros de Shopping del Sol</t>
+          <t>InfoCasas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -33086,12 +33146,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Ycua Satí</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3 dormitorios</t>
+          <t>1 dormitorio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -33106,12 +33166,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>750</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -33121,7 +33181,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>InfoCasas — a metros de Shopping del Sol</t>
+          <t>InfoCasas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -33138,12 +33198,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Luis A. de Herrera</t>
+          <t>Ycua Satí</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1 dormitorio</t>
+          <t>2 dormitorios</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -33158,12 +33218,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -33190,12 +33250,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Luis A. de Herrera</t>
+          <t>Ycua Satí</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1 dormitorio</t>
+          <t>2 dormitorios</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -33210,12 +33270,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -33225,7 +33285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>InfoCasas / RE/MAX</t>
+          <t>InfoCasas — Torre Eminent, referencia de techo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -33242,17 +33302,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Luis A. de Herrera</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2 dormitorios</t>
+          <t>1 dormitorio</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tradicional (sin muebles)</t>
+          <t>Amoblado (largo plazo)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -33262,12 +33322,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>650</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -33277,7 +33337,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>InfoCasas</t>
+          <t>InfoCasas — a metros de Shopping del Sol</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -33294,57 +33354,317 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3 dormitorios</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>InfoCasas — a metros de Shopping del Sol</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Luis A. de Herrera</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1 dormitorio</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>InfoCasas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Luis A. de Herrera</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1 dormitorio</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>InfoCasas / RE/MAX</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Luis A. de Herrera</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2 dormitorios</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>InfoCasas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Luis A. de Herrera</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>3 dormitorios</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Amoblado (largo plazo)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>USD/mes</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>InfoCasas / MercadoProp / Red Exclusivos</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vista Alegre</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Monoambiente</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>InfoCasas — zona de referencia mas economica, dato puntual, no rango</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J16"/>
+  <autoFilter ref="A1:J21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
+++ b/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
@@ -9,11 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen (con dato real)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categoria de Zona" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen (con dato real)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$793</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Resumen (con dato real)'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categoria de Zona'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Resumen (con dato real)'!$A$1:$J$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +41,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +66,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -77,12 +85,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -532,7 +541,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cobertura actual (2026-08-16): 5 de 66 barrios con datos reales de categoría C (Villa Morra, Luis A. de Herrera, Las Lomas, Recoleta, Mburucuyá) — los 61 restantes están con categoría D (pendiente), estructura lista para completar.</t>
+          <t>Cobertura actual (2026-08-16): 8 de 66 barrios con datos reales de categoría C (Villa Morra, Luis A. de Herrera, Las Lomas, Recoleta, Mburucuyá, Ycuá Satí, Vista Alegre, Salvador del Mundo) — los 58 restantes están con categoría D (pendiente), estructura lista para completar.</t>
         </is>
       </c>
     </row>
@@ -541,6 +550,16 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>Hoja 'Categoria de Zona' (nueva): clasifica cada barrio por tipo de zona (Residencial / Comercial / Zona Shopping / Eje Corporativo / Mixta) y una marca de rentabilidad relativa donde ya hay evidencia — pedido explícito del founder. Barrio Herrera está confirmado como categoría A (dato directo del founder); el resto es inferencia propia (categoría C), a confirmar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Fuente original: primera carga hecha para el caso contracts/cases/HERRERA-001/, ver 17-tabla-tarifas-por-barrio.md de ese caso y knowledge-base/investment/07-tarifas-por-barrio-asuncion.md para el detalle metodológico completo.</t>
         </is>
@@ -32556,6 +32575,363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="90" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Barrio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Categoria de zona</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Rentabilidad relativa</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Categoria de dato</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha de actualizacion</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Luis A. de Herrera</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Founder, 2026-08-16</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Confirmado por el founder: barrio residencial con demanda real de 3 dormitorios amoblados; cercano y con vías de acceso a los principales centros comerciales, sin estar en medio del tránsito/ruido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Villa Morra</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Eje Corporativo / Mixta (residencial-comercial)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inferencia propia + founder (13-...md §2)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zona corporativa consolidada, alta densidad de oficinas y locales junto a torres residenciales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mburucuyá</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Eje Corporativo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inferencia propia + founder (13-...md §2)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Corredor corporativo nombrado explícitamente por el founder como 'Eje Corporativo'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Comercial / Zona Shopping</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inferencia propia + founder (13-...md §2)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A metros de Shopping del Sol, alta densidad comercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Las Lomas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Residencial (exclusivo)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inferencia propia + founder (13-...md §2)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nombrado explícitamente por el founder como zona de referencia de plusvalía; uno de los barrios más exclusivos de Asunción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ycua Satí</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Residencial / Mixta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Media-Alta (sin confirmar)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Inferencia propia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Zona residencial consolidada, cercana a Villa Morra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vista Alegre</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Residencial (más económica)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Inferencia propia</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Referencia de zona más económica dentro del relevamiento — usada para contraste, no como zona premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Salvador del Mundo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Residencial / Mixta</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Inferencia propia</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Zona residencial consolidada.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
+++ b/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$793</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categoria de Zona'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Resumen (con dato real)'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categoria de Zona'!$A$1:$J$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Resumen (con dato real)'!$A$1:$J$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +41,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,12 +66,6 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -85,13 +79,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -551,7 +544,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hoja 'Categoria de Zona' (nueva): clasifica cada barrio por tipo de zona (Residencial / Comercial / Zona Shopping / Eje Corporativo / Mixta) y una marca de rentabilidad relativa donde ya hay evidencia — pedido explícito del founder. Barrio Herrera está confirmado como categoría A (dato directo del founder); el resto es inferencia propia (categoría C), a confirmar.</t>
+          <t>Hoja 'Categoria de Zona': clasifica cada barrio por tipo de zona (Residencial / Comercial / Zona Shopping / Eje Corporativo / Mixta / Emergente), con un ranking basado en fuentes reales del mercado inmobiliario paraguayo (Yulia Traidova, Inmovia, Revista FOCO). IMPORTANTE: plusvalía y rentabilidad de alquiler son columnas SEPARADAS, nunca combinadas — plusvalía es ganancia de capital realizada en la venta (precio de venta menos precio de compra, anualizada sobre el tiempo de tenencia); rentabilidad de alquiler es el retorno de renta sobre el valor de compra, mientras se tiene la propiedad (ver hoja Datos). Barrio Herrera es el único con plusvalía confirmada en categoría A (dato directo del founder); el resto del ranking es categoría C (fuentes de terceros), a confirmar.</t>
         </is>
       </c>
     </row>
@@ -11352,14 +11345,26 @@
           <t>USD/mes</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>InfoCasas/Clasipar — incluye el sector 'Carmelitas' (confirmado por el founder como parte de Las Lomas, no barrio aparte)</t>
+        </is>
+      </c>
       <c r="I268" t="inlineStr">
         <is>
           <t>2026-08-16</t>
@@ -11367,7 +11372,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Pendiente de relevar.</t>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
@@ -32575,16 +32580,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="90" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="90" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32600,25 +32608,40 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Rentabilidad relativa</t>
+          <t>Precio m2 de referencia</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Plusvalia de zona (ganancia de capital en la venta)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Rentabilidad de alquiler tipica de zona (renta sobre valor de compra)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Ranking del estudio</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>Categoria de dato</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Fecha de actualizacion</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -32627,37 +32650,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Luis A. de Herrera</t>
+          <t>Manorá</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Residencial en expansión / Emergente</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>USD 786/m2 (el más alto de Asunción)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Alta — mencionado como la zona de mayor crecimiento y apreciación de la ciudad</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Founder, 2026-08-16</t>
+          <t>Sin dato específico relevado todavía</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Confirmado por el founder: barrio residencial con demanda real de 3 dormitorios amoblados; cercano y con vías de acceso a los principales centros comerciales, sin estar en medio del tránsito/ruido.</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yulia Traidova (precios por barrio 2026), Inmovia</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Zona originalmente residencial de clase media, en expansión acelerada con decenas de torres nuevas — el barrio de mayor precio/m2 de la ciudad según el estudio.</t>
         </is>
       </c>
     </row>
@@ -32674,254 +32712,515 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+          <t>USD 748/m2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Alta — zona consolidada; algunos proyectos publicitan hasta 25% de plusvalía estimada</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6-10% bruto anual (rango general de la ciudad); proyectos puntuales publicitan hasta 15%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Inferencia propia + founder (13-...md §2)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Zona corporativa consolidada, alta densidad de oficinas y locales junto a torres residenciales.</t>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yulia Traidova, InfoCasas (tarifas reales ya relevadas)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>El barrio más consolidado y prestigioso de Asunción — mayor concentración de oficinas corporativas, shopping de lujo y torres residenciales premium. Perfil de inversor conservador (estabilidad, bajo riesgo).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mburucuyá</t>
+          <t>Las Lomas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eje Corporativo</t>
+          <t>Residencial (exclusivo)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+          <t>USD 742/m2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Alta — junto con Villa Morra y Carmelitas, de las zonas más valoradas de la ciudad</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Inferencia propia + founder (13-...md §2)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Corredor corporativo nombrado explícitamente por el founder como 'Eje Corporativo'.</t>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yulia Traidova, Revista FOCO ('las 5 zonas más top de Asunción')</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Incluye el sector conocido comercialmente como 'Carmelitas' (cercano a la capilla/convento Las Carmelitas Descalzas) — mismo barrio, no uno separado, confirmado por el founder.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Mcal. López</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Comercial / Zona Shopping</t>
+          <t>Residencial / Comercial (avenida principal)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+          <t>USD 713/m2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Inferencia propia + founder (13-...md §2)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>A metros de Shopping del Sol, alta densidad comercial.</t>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yulia Traidova</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Corresponde a la zona colloquialmente citada como 'Mariscal López' en estudios de mercado — avenida principal con alta densidad comercial y residencial.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Las Lomas</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Residencial (exclusivo)</t>
+          <t>Comercial / Zona Shopping</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alta (plusvalía &gt;20%/año, dato del founder)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+          <t>USD 663/m2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Alta — barrio preferido por familias, en crecimiento sostenido</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Inferencia propia + founder (13-...md §2)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Nombrado explícitamente por el founder como zona de referencia de plusvalía; uno de los barrios más exclusivos de Asunción.</t>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yulia Traidova, InfoCasas (tarifas reales ya relevadas)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>El barrio preferido por familias paraguayas y extranjeros que se relocalizan — buen balance entre calidad de vida y retorno de inversión, según el estudio.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ycua Satí</t>
+          <t>Luis A. de Herrera</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Residencial / Mixta</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Media-Alta (sin confirmar)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>Sin dato específico de precio m2 (referencia venta zona USD 1.750-2.100/m2, `03-...md`)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Alta — plusvalía &gt;20%/año confirmada directamente por el founder</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Inferencia propia</t>
+          <t>Confirmado con dato real: ver hoja 'Datos' — 1/2/3 dormitorios</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>6 (no rankeado en los estudios externos, pero confirmado como zona de alta demanda por el founder)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zona residencial consolidada, cercana a Villa Morra.</t>
+          <t>A (plusvalía, demanda) / C (ranking relativo)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Founder, 2026-08-16 + `13-...md` §2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Confirmado por el founder: barrio residencial con demanda real de 3 dormitorios amoblados; cercano y con vías de acceso a los principales centros comerciales, sin estar en medio del tránsito/ruido.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vista Alegre</t>
+          <t>Santísima Trinidad</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Residencial (más económica)</t>
+          <t>Emergente</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mencionado como 'la zona emergente por excelencia' de Asunción</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Emergente, sin rankear con las zonas top</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Inferencia propia</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Referencia de zona más económica dentro del relevamiento — usada para contraste, no como zona premium.</t>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Inmovia ('7 mejores barrios para invertir')</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Corresponde a la zona citada como 'Trinidad' en estudios de mercado.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Mburucuyá</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Eje Corporativo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Alta — corredor de mayor desarrollo vertical de la ciudad</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Alta demanda de renta residencial y temporal/Airbnb, mayor volumen de oferta nueva</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Alto (corredor corporativo)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Founder (13-...md §2), Inmovia ('The Corporate Hub')</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Corredor corporativo nombrado explícitamente por el founder como 'Eje Corporativo' — coincide con lo que estudios externos llaman 'The Corporate Hub', el área de mayor desarrollo vertical de la ciudad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ycua Satí</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Residencial / Mixta</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mencionado junto a Villa Morra/Jara como zona de mayor valorización actual</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Alto (mencionado junto a las zonas top)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Departamentosasuncion.com</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Zona residencial consolidada, cercana a Villa Morra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vista Alegre</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Residencial (más económica)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bajo (zona de referencia económica, no premium)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Inferencia propia</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Referencia de zona más económica dentro del relevamiento — usada para contraste, no como zona premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Salvador del Mundo</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Residencial / Mixta</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sin dato específico relevado todavía</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sin rankear todavía</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Inferencia propia</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Zona residencial consolidada.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:J12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32932,7 +33231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -33215,12 +33514,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 dormitorio</t>
+          <t>Monoambiente</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tradicional (sin muebles)</t>
+          <t>Amoblado (largo plazo)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -33230,12 +33529,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>390</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>750</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -33245,7 +33544,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>InfoCasas</t>
+          <t>InfoCasas/Clasipar — incluye el sector 'Carmelitas' (confirmado por el founder como parte de Las Lomas, no barrio aparte)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -33267,12 +33566,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2 dormitorios</t>
+          <t>1 dormitorio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amoblado (largo plazo)</t>
+          <t>Tradicional (sin muebles)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -33282,12 +33581,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -33314,32 +33613,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Villa Morra</t>
+          <t>Las Lomas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Monoambiente</t>
+          <t>2 dormitorios</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Airbnb / temporal</t>
+          <t>Amoblado (largo plazo)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>USD/noche</t>
+          <t>USD/mes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -33349,7 +33648,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Airbnb (listados directos)</t>
+          <t>InfoCasas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -33376,22 +33675,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amoblado (largo plazo)</t>
+          <t>Airbnb / temporal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>USD/mes</t>
+          <t>USD/noche</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -33401,7 +33700,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>InfoCasas</t>
+          <t>Airbnb (listados directos)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -33423,7 +33722,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2 dormitorios</t>
+          <t>Monoambiente</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -33438,12 +33737,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>800</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1800</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -33475,7 +33774,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3 dormitorios</t>
+          <t>2 dormitorios</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -33490,12 +33789,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -33522,12 +33821,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ycua Satí</t>
+          <t>Villa Morra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1 dormitorio</t>
+          <t>3 dormitorios</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -33542,12 +33841,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -33579,12 +33878,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2 dormitorios</t>
+          <t>1 dormitorio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tradicional (sin muebles)</t>
+          <t>Amoblado (largo plazo)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -33594,12 +33893,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>750</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -33636,7 +33935,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amoblado (largo plazo)</t>
+          <t>Tradicional (sin muebles)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -33646,12 +33945,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -33661,7 +33960,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>InfoCasas — Torre Eminent, referencia de techo</t>
+          <t>InfoCasas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -33678,12 +33977,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Ycua Satí</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1 dormitorio</t>
+          <t>2 dormitorios</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -33698,12 +33997,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -33713,7 +34012,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>InfoCasas — a metros de Shopping del Sol</t>
+          <t>InfoCasas — Torre Eminent, referencia de techo</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -33735,7 +34034,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3 dormitorios</t>
+          <t>1 dormitorio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -33750,12 +34049,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>650</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -33782,17 +34081,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Luis A. de Herrera</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1 dormitorio</t>
+          <t>3 dormitorios</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tradicional (sin muebles)</t>
+          <t>Amoblado (largo plazo)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -33802,12 +34101,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -33817,7 +34116,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>InfoCasas</t>
+          <t>InfoCasas — a metros de Shopping del Sol</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -33844,7 +34143,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amoblado (largo plazo)</t>
+          <t>Tradicional (sin muebles)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -33854,12 +34153,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -33869,7 +34168,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>InfoCasas / RE/MAX</t>
+          <t>InfoCasas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -33891,12 +34190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 dormitorios</t>
+          <t>1 dormitorio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tradicional (sin muebles)</t>
+          <t>Amoblado (largo plazo)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -33906,14 +34205,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
           <t>C</t>
@@ -33921,7 +34220,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>InfoCasas</t>
+          <t>InfoCasas / RE/MAX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -33943,12 +34242,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 dormitorios</t>
+          <t>2 dormitorios</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amoblado (largo plazo)</t>
+          <t>Tradicional (sin muebles)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -33958,12 +34257,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -33973,7 +34272,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>InfoCasas / MercadoProp / Red Exclusivos</t>
+          <t>InfoCasas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -33990,57 +34289,109 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Luis A. de Herrera</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3 dormitorios</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>InfoCasas / MercadoProp / Red Exclusivos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Vista Alegre</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Monoambiente</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Amoblado (largo plazo)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>USD/mes</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>InfoCasas — zona de referencia mas economica, dato puntual, no rango</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
+  <autoFilter ref="A1:J22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
+++ b/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
@@ -10,12 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categoria de Zona" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen (con dato real)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distritos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen (con dato real)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$793</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categoria de Zona'!$A$1:$J$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Resumen (con dato real)'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categoria de Zona'!$A$1:$L$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resumen (con dato real)'!$A$1:$J$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -544,7 +545,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hoja 'Categoria de Zona': clasifica cada barrio por tipo de zona (Residencial / Comercial / Zona Shopping / Eje Corporativo / Mixta / Emergente), con un ranking basado en fuentes reales del mercado inmobiliario paraguayo (Yulia Traidova, Inmovia, Revista FOCO). IMPORTANTE: plusvalía y rentabilidad de alquiler son columnas SEPARADAS, nunca combinadas — plusvalía es ganancia de capital realizada en la venta (precio de venta menos precio de compra, anualizada sobre el tiempo de tenencia); rentabilidad de alquiler es el retorno de renta sobre el valor de compra, mientras se tiene la propiedad (ver hoja Datos). Barrio Herrera es el único con plusvalía confirmada en categoría A (dato directo del founder); el resto del ranking es categoría C (fuentes de terceros), a confirmar.</t>
+          <t>Hoja 'Categoria de Zona': ranking de 21 barrios (de 66) con fuentes reales del mercado inmobiliario paraguayo (Place Analyzer/infonegocios.com.py, Yulia Traidova, Capadei, Inmovia, Revista FOCO). IMPORTANTE, dos separaciones que nunca se mezclan: (1) precio de TERRENO (Place Analyzer) vs. precio de DEPARTAMENTO (Yulia Traidova y otras fuentes) son columnas distintas, no intercambiables; (2) plusvalía (ganancia de capital, en la venta) y rentabilidad de alquiler (retorno de renta, mientras se tiene la propiedad, ver hoja Datos) tampoco se combinan. Barrio Herrera es el único con plusvalía confirmada en categoría A (dato directo del founder); el resto del ranking es categoría C (fuentes de terceros), a confirmar.</t>
         </is>
       </c>
     </row>
@@ -553,6 +554,16 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
+        <is>
+          <t>Hoja 'Distritos': los 6 distritos oficiales de Asunción (La Recoleta, Santísima Trinidad, San Roque, La Encarnación, La Catedral, Santa María) que agrupan los 66-68 barrios de la ciudad (fuentes externas citan 68, el plano del founder tiene 66 — discrepancia sin conciliar). La columna 'Distrito' de la hoja Categoria de Zona solo está completa para los barrios con evidencia razonable (ej. vecindad geográfica descripta en fuentes) — el resto queda pendiente, no se asume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Fuente original: primera carga hecha para el caso contracts/cases/HERRERA-001/, ver 17-tabla-tarifas-por-barrio.md de ese caso y knowledge-base/investment/07-tarifas-por-barrio-asuncion.md para el detalle metodológico completo.</t>
         </is>
@@ -32580,19 +32591,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="90" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="90" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32603,45 +32616,55 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Distrito</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Categoria de zona</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Precio m2 de referencia</t>
-        </is>
-      </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Precio terreno m2 (Place Analyzer)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Precio departamento m2 (referencia)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Plusvalia de zona (ganancia de capital en la venta)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Rentabilidad de alquiler tipica de zona (renta sobre valor de compra)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Ranking del estudio</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Categoria de dato</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Fecha de actualizacion</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -32655,47 +32678,57 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Residencial en expansión / Emergente</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>USD 786/m2 (el más alto de Asunción)</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alta — mencionado como la zona de mayor crecimiento y apreciación de la ciudad</t>
+          <t>USD 786/m² (el más alto de Asunción)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>USD 1.633-2.400/m² (rango amplio entre fuentes, sin conciliar)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Alta — zona de mayor crecimiento y apreciación</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Yulia Traidova (precios por barrio 2026), Inmovia</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Zona originalmente residencial de clase media, en expansión acelerada con decenas de torres nuevas — el barrio de mayor precio/m2 de la ciudad según el estudio.</t>
+          <t>Place Analyzer/infonegocios.com.py, Yulia Traidova, Capadei</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Rango de precio de depto muy disperso entre fuentes (USD 1.633-1.784 vs. USD 1.800-2.400) — no conciliado, se muestra el rango completo.</t>
         </is>
       </c>
     </row>
@@ -32707,47 +32740,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eje Corporativo / Mixta (residencial-comercial)</t>
+          <t>La Recoleta</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USD 748/m2</t>
+          <t>Eje Corporativo / Mixta</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alta — zona consolidada; algunos proyectos publicitan hasta 25% de plusvalía estimada</t>
+          <t>USD 748/m²</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6-10% bruto anual (rango general de la ciudad); proyectos puntuales publicitan hasta 15%</t>
+          <t>USD 1.698-2.500/m² (según antigüedad de la muestra)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Alta — zona consolidada, algunos proyectos publicitan hasta 25%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6-10% bruto anual; proyectos puntuales publicitan hasta 15%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yulia Traidova, InfoCasas (tarifas reales ya relevadas)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>El barrio más consolidado y prestigioso de Asunción — mayor concentración de oficinas corporativas, shopping de lujo y torres residenciales premium. Perfil de inversor conservador (estabilidad, bajo riesgo).</t>
+          <t>Place Analyzer/infonegocios.com.py, Yulia Traidova, Capadei, InfoCasas (tarifas reales)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>El barrio más consolidado y prestigioso — mayor concentración de oficinas corporativas, shopping de lujo y torres residenciales premium.</t>
         </is>
       </c>
     </row>
@@ -32759,47 +32802,57 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Residencial (exclusivo)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>USD 742/m2</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alta — junto con Villa Morra y Carmelitas, de las zonas más valoradas de la ciudad</t>
+          <t>USD 742/m²</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>USD 1.800-2.300/m² (incluye el sector Carmelitas)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yulia Traidova, Revista FOCO ('las 5 zonas más top de Asunción')</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Incluye el sector conocido comercialmente como 'Carmelitas' (cercano a la capilla/convento Las Carmelitas Descalzas) — mismo barrio, no uno separado, confirmado por el founder.</t>
+          <t>Place Analyzer/infonegocios.com.py, Capadei</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Incluye el sector 'Carmelitas' (cercano a la capilla/convento Las Carmelitas Descalzas) — mismo barrio, confirmado por el founder.</t>
         </is>
       </c>
     </row>
@@ -32811,47 +32864,57 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>La Recoleta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Residencial / Comercial (avenida principal)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>USD 713/m2</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>USD 713/m²</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sin dato específico de departamento</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sin dato específico relevado todavía</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yulia Traidova</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Corresponde a la zona colloquialmente citada como 'Mariscal López' en estudios de mercado — avenida principal con alta densidad comercial y residencial.</t>
+          <t>Place Analyzer/infonegocios.com.py</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Corresponde a 'Mariscal Francisco Solano López' en la fuente original — avenida principal de alta densidad comercial/residencial.</t>
         </is>
       </c>
     </row>
@@ -32863,203 +32926,235 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>La Recoleta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Comercial / Zona Shopping</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>USD 663/m2</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alta — barrio preferido por familias, en crecimiento sostenido</t>
+          <t>USD 663/m²</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>Sin dato específico de departamento</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Alta — barrio preferido por familias</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yulia Traidova, InfoCasas (tarifas reales ya relevadas)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>El barrio preferido por familias paraguayas y extranjeros que se relocalizan — buen balance entre calidad de vida y retorno de inversión, según el estudio.</t>
+          <t>Place Analyzer/infonegocios.com.py, InfoCasas (tarifas reales)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>A metros de Shopping del Sol, alta densidad comercial.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Luis A. de Herrera</t>
+          <t>San Jorge</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Residencial</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sin dato específico de precio m2 (referencia venta zona USD 1.750-2.100/m2, `03-...md`)</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alta — plusvalía &gt;20%/año confirmada directamente por el founder</t>
+          <t>USD 662/m²</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Confirmado con dato real: ver hoja 'Datos' — 1/2/3 dormitorios</t>
+          <t>Sin dato específico</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6 (no rankeado en los estudios externos, pero confirmado como zona de alta demanda por el founder)</t>
+          <t>Sin dato específico</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A (plusvalía, demanda) / C (ranking relativo)</t>
+          <t>Sin dato específico</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Founder, 2026-08-16 + `13-...md` §2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Confirmado por el founder: barrio residencial con demanda real de 3 dormitorios amoblados; cercano y con vías de acceso a los principales centros comerciales, sin estar en medio del tránsito/ruido.</t>
-        </is>
-      </c>
+          <t>Place Analyzer/infonegocios.com.py</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Santísima Trinidad</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emergente</t>
+          <t>La Recoleta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mencionado como 'la zona emergente por excelencia' de Asunción</t>
+          <t>USD 656/m²</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>Sin dato específico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Emergente, sin rankear con las zonas top</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+          <t>Mencionado entre las zonas de mayor precio promedio (junto a Mburucuyá/Villa Morra/Manorá)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Inmovia ('7 mejores barrios para invertir')</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Corresponde a la zona citada como 'Trinidad' en estudios de mercado.</t>
-        </is>
-      </c>
+          <t>Place Analyzer/infonegocios.com.py, Capadei</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mburucuyá</t>
+          <t>Mcal. Estigarribia</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eje Corporativo</t>
+          <t>La Recoleta</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Alta — corredor de mayor desarrollo vertical de la ciudad</t>
+          <t>USD 618/m²</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alta demanda de renta residencial y temporal/Airbnb, mayor volumen de oferta nueva</t>
+          <t>Sin dato específico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Alto (corredor corporativo)</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Founder (13-...md §2), Inmovia ('The Corporate Hub')</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Corredor corporativo nombrado explícitamente por el founder como 'Eje Corporativo' — coincide con lo que estudios externos llaman 'The Corporate Hub', el área de mayor desarrollo vertical de la ciudad.</t>
+          <t>Place Analyzer/infonegocios.com.py</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Corresponde a 'Mariscal José Félix Estigarribia' en la fuente original.</t>
         </is>
       </c>
     </row>
@@ -33071,161 +33166,985 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Residencial / Mixta</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sin dato específico relevado todavía</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mencionado junto a Villa Morra/Jara como zona de mayor valorización actual</t>
+          <t>USD 613/m²</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>Referencia tarifas reales ya relevadas (ver hoja Datos)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Alto (mencionado junto a las zonas top)</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+          <t>Mencionado entre las zonas de mayor precio promedio</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Departamentosasuncion.com</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Zona residencial consolidada, cercana a Villa Morra.</t>
-        </is>
-      </c>
+          <t>Place Analyzer/infonegocios.com.py, InfoCasas (tarifas reales)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vista Alegre</t>
+          <t>Madame Lynch</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Residencial (más económica)</t>
+          <t>D - pendiente de confirmar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>USD 602/m²</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sin dato específico relevado todavía</t>
+          <t>Sin dato específico</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bajo (zona de referencia económica, no premium)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Inferencia propia</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Referencia de zona más económica dentro del relevamiento — usada para contraste, no como zona premium.</t>
+          <t>Place Analyzer/infonegocios.com.py</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Corresponde a 'Madame Elisa Alicia Lynch' en la fuente original.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Mburucuyá</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Eje Corporativo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sin dato específico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Alta — corredor de mayor desarrollo vertical, mencionado entre las zonas de mayor precio promedio</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alta demanda de renta residencial y Airbnb</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Alto (corredor corporativo, sin ranking numérico de Place Analyzer)</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Founder (13-...md §2), Capadei, Inmovia ('The Corporate Hub')</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Corredor corporativo nombrado explícitamente por el founder como 'Eje Corporativo'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Luis A. de Herrera</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sin dato específico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Referencia venta zona USD 1.750-2.100/m² (`03-...md`)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Alta — &gt;20%/año, confirmada directamente por el founder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Confirmado con dato real, ver hoja Datos</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sin ranking numérico externo (no aparece en Place Analyzer ni Yulia Traidova) — confirmado por el founder como caso activo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>A (plusvalía, demanda) / C (ranking relativo)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Founder, 2026-08-16 + `13-...md` §2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Confirmado por el founder: barrio residencial con demanda real de 3 dormitorios amoblados; cercano a los principales centros comerciales sin estar en medio del tránsito/ruido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Santísima Trinidad</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Santísima Trinidad</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Emergente / Comercial</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sin dato específico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>USD 900-1.300/m²</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mencionado como 'la zona emergente por excelencia'</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Emergente, sin ranking numérico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Inmovia ('7 mejores barrios para invertir'), Yulia Traidova</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Da nombre a uno de los 6 distritos de Asunción, además de ser barrio propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jara</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Residencial consolidado</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sin dato específico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>USD 987-1.125/m² (subió en el período relevado)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Positiva — mencionado con suba de precio</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sin ranking numérico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Capadei</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Residencial en desarrollo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sin dato específico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>USD 900-1.200/m²</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>En desarrollo, precios accesibles</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Zona en desarrollo, no premium</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Yulia Traidova</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Residencial económico</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sin dato específico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>USD 800-1.100/m²</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Económico, cerca del centro</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Zona económica</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Yulia Traidova</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Vista Alegre</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Residencial (más económica)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sin dato específico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Referencia tarifas reales ya relevadas (ver hoja Datos)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bajo (zona de referencia económica)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>InfoCasas (tarifas reales), inferencia propia</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Salvador del Mundo</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Residencial / Mixta</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Sin dato específico relevado todavía</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Sin dato específico relevado todavía</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Sin dato específico relevado todavía</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Sin rankear todavía</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sin dato específico de Place Analyzer</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Referencia tarifas reales ya relevadas (ver hoja Datos)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sin rankear</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Inferencia propia</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Zona residencial consolidada.</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>InfoCasas (tarifas reales)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Zeballos Cué</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Económico / En expansión</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>USD 101/m² (entre los 5 más económicos de la ciudad)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>USD 800-1.000/m²</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Potencial de valorización (zona en expansión, precio de partida bajo)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>62 (entre los más económicos de la ciudad — referencia de piso, no de techo)</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Place Analyzer/infonegocios.com.py, Yulia Traidova</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Banco San Miguel</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Económico</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>USD 129/m² (entre los 5 más económicos de la ciudad)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>63 (entre los más económicos de la ciudad)</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Place Analyzer/infonegocios.com.py</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Económico</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>USD 94/m² (el más económico de la ciudad)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>66 (el más económico de la ciudad, según Place Analyzer)</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Place Analyzer/infonegocios.com.py</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J12"/>
+  <autoFilter ref="A1:L22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Distrito</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Categoria de dato</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha de actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>La Recoleta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Zona noreste/este, incluye el corredor Villa Morra-Recoleta-Mburucuya (Eje Corporativo)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A (confirmado, multiples fuentes)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Founder + Wikipedia/lamberweb.com/homy.com.py</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Santísima Trinidad</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zona norte</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A (confirmado, multiples fuentes)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Founder + Wikipedia/lamberweb.com/homy.com.py</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>San Roque</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Zona centro, parte del casco historico</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A (confirmado, multiples fuentes)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Founder + Wikipedia/lamberweb.com/homy.com.py</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>La Encarnación</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Zona centro, parte del casco historico</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A (confirmado, multiples fuentes)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Founder + Wikipedia/lamberweb.com/homy.com.py</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>La Catedral</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Zona centro/costa, casco historico y microcentro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A (confirmado, multiples fuentes)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Founder + Wikipedia/lamberweb.com/homy.com.py</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Santa María</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Zona sur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A (confirmado, multiples fuentes)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Founder + Wikipedia/lamberweb.com/homy.com.py</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
+++ b/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen (con dato real)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$793</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categoria de Zona'!$A$1:$L$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$817</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categoria de Zona'!$A$1:$L$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resumen (con dato real)'!$A$1:$J$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J793"/>
+  <dimension ref="A1:J817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -32579,8 +32579,968 @@
         </is>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Monoambiente</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Airbnb / temporal</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>USD/noche</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr"/>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr"/>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Monoambiente</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr"/>
+      <c r="G795" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr"/>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Monoambiente</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr"/>
+      <c r="F796" t="inlineStr"/>
+      <c r="G796" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr"/>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>1 dormitorio</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Airbnb / temporal</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>USD/noche</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr"/>
+      <c r="F797" t="inlineStr"/>
+      <c r="G797" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr"/>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>1 dormitorio</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr"/>
+      <c r="F798" t="inlineStr"/>
+      <c r="G798" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr"/>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>1 dormitorio</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="inlineStr"/>
+      <c r="G799" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr"/>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2 dormitorios</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Airbnb / temporal</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>USD/noche</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="inlineStr"/>
+      <c r="G800" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>2 dormitorios</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="inlineStr"/>
+      <c r="G801" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr"/>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>2 dormitorios</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="inlineStr"/>
+      <c r="G802" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr"/>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>3 dormitorios</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Airbnb / temporal</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>USD/noche</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr"/>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>3 dormitorios</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="inlineStr"/>
+      <c r="G804" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr"/>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>3 dormitorios</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="inlineStr"/>
+      <c r="G805" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr"/>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Monoambiente</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Airbnb / temporal</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>USD/noche</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr"/>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Monoambiente</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="inlineStr"/>
+      <c r="G807" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr"/>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Monoambiente</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="inlineStr"/>
+      <c r="G808" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr"/>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>1 dormitorio</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Airbnb / temporal</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>USD/noche</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr"/>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>1 dormitorio</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="inlineStr"/>
+      <c r="G810" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr"/>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>1 dormitorio</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr"/>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>2 dormitorios</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Airbnb / temporal</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>USD/noche</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr"/>
+      <c r="G812" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr"/>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>2 dormitorios</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr"/>
+      <c r="G813" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr"/>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>2 dormitorios</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>3 dormitorios</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Airbnb / temporal</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>USD/noche</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr"/>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>3 dormitorios</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Tradicional (sin muebles)</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr"/>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>3 dormitorios</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr"/>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>Pendiente de relevar.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J793"/>
+  <autoFilter ref="A1:J817"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32591,7 +33551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -33358,7 +34318,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sin dato específico de Place Analyzer</t>
+          <t>USD 1.200-1.500/m² (listados de mercado, NO Place Analyzer — ver nota)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -33378,17 +34338,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sin ranking numérico externo (no aparece en Place Analyzer ni Yulia Traidova) — confirmado por el founder como caso activo</t>
+          <t>Sin ranking numérico de Place Analyzer — confirmado por el founder como caso activo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>A (plusvalía, demanda) / C (ranking relativo)</t>
+          <t>A (plusvalía, demanda) / C (precio terreno, ranking relativo)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Founder, 2026-08-16 + `13-...md` §2</t>
+          <t>Founder, 2026-08-16 + `13-...md` §2; precio terreno: InfoCasas/Coldwell Banker/Red Exclusivos (listados activos, 2026-08-17)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -33398,7 +34358,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Confirmado por el founder: barrio residencial con demanda real de 3 dormitorios amoblados; cercano a los principales centros comerciales sin estar en medio del tránsito/ruido.</t>
+          <t>Confirmado por el founder: barrio residencial con demanda real de 3 dormitorios amoblados; cercano a los principales centros comerciales sin estar en medio del tránsito/ruido. El precio de terreno de USD 1.200-1.500/m² es de LISTADOS DE MERCADO (asking price), no del algoritmo de Place Analyzer -- metodologia distinta, no comparar directamente contra el ranking de la seccion 3. El terreno del trato ($360.000 / 469 m² = USD 767,59/m²) queda POR DEBAJO de este rango de listados actuales -- refuerza que el trato es favorable.</t>
         </is>
       </c>
     </row>
@@ -33908,7 +34868,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>66 (el más económico de la ciudad, según Place Analyzer)</t>
+          <t>68 (el más económico de la ciudad, según Place Analyzer — actualizado tras corrección a 68 barrios)</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -33928,8 +34888,132 @@
       </c>
       <c r="L22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jukyty</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Económico</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>USD 142/m²</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>64 (entre los más económicos)</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Place Analyzer/infonegocios.com.py</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>No estaba en la transcripción original del plano de 66 barrios — hipótesis razonable (no confirmada) de que sea uno de los 2 barrios faltantes tras la corrección a 68.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>San Cayetano</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D - pendiente de confirmar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Económico</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>USD 113/m²</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sin dato específico</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>65 (entre los más económicos)</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Place Analyzer/infonegocios.com.py</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>No estaba en la transcripción original del plano de 66 barrios — misma hipótesis que Jukyty, no confirmada.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L22"/>
+  <autoFilter ref="A1:L24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
+++ b/knowledge-base/investment/data/tarifas-alquiler-por-barrio-asuncion.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$817</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Categoria de Zona'!$A$1:$L$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resumen (con dato real)'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resumen (con dato real)'!$A$1:$J$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21980,14 +21980,26 @@
           <t>USD/noche</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr"/>
-      <c r="F530" t="inlineStr"/>
-      <c r="G530" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H530" t="inlineStr"/>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G530" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Airbnb.com (listados reales dentro del barrio) — primer corte, solo 2 listados con precio</t>
+        </is>
+      </c>
       <c r="I530" t="inlineStr">
         <is>
           <t>2026-08-16</t>
@@ -21995,7 +22007,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>Pendiente de relevar.</t>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
@@ -35234,7 +35246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -36141,27 +36153,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 dormitorio</t>
+          <t>Monoambiente</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tradicional (sin muebles)</t>
+          <t>Airbnb / temporal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>USD/mes</t>
+          <t>USD/noche</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -36171,7 +36183,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>InfoCasas</t>
+          <t>Airbnb.com (listados reales dentro del barrio) — primer corte, solo 2 listados con precio</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -36198,7 +36210,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Amoblado (largo plazo)</t>
+          <t>Tradicional (sin muebles)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -36208,12 +36220,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>560</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -36223,7 +36235,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>InfoCasas / RE/MAX</t>
+          <t>InfoCasas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -36245,12 +36257,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2 dormitorios</t>
+          <t>1 dormitorio</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tradicional (sin muebles)</t>
+          <t>Amoblado (largo plazo)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -36260,14 +36272,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>C</t>
@@ -36275,7 +36287,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>InfoCasas</t>
+          <t>InfoCasas / RE/MAX</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -36297,12 +36309,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3 dormitorios</t>
+          <t>2 dormitorios</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amoblado (largo plazo)</t>
+          <t>Tradicional (sin muebles)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -36312,12 +36324,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -36327,7 +36339,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>InfoCasas / MercadoProp / Red Exclusivos</t>
+          <t>InfoCasas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -36344,57 +36356,109 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Luis A. de Herrera</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3 dormitorios</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Amoblado (largo plazo)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>InfoCasas / MercadoProp / Red Exclusivos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Vista Alegre</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Monoambiente</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Amoblado (largo plazo)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>USD/mes</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>USD/mes</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>InfoCasas — zona de referencia mas economica, dato puntual, no rango</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Primer corte via busqueda web, 2026-08-15/16 — no es relevamiento exhaustivo ni tasacion profesional.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J22"/>
+  <autoFilter ref="A1:J23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>